--- a/artfynd/A 61377-2025 artfynd.xlsx
+++ b/artfynd/A 61377-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>130734160</v>
+        <v>130734161</v>
       </c>
       <c r="B2" t="n">
-        <v>79211</v>
+        <v>79219</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -713,10 +713,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>444917</v>
+        <v>444973</v>
       </c>
       <c r="R2" t="n">
-        <v>7052302</v>
+        <v>7052318</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -749,11 +749,6 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2026-01-16</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Relativt rikligt med garnlav på gran.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -769,6 +764,11 @@
       <c r="AH2" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AI2" t="inlineStr">
+        <is>
+          <t>Grandominerad äldre flerskiktad skog med inslag av björk.</t>
         </is>
       </c>
       <c r="AJ2" t="inlineStr">
@@ -806,10 +806,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>130734161</v>
+        <v>130734160</v>
       </c>
       <c r="B3" t="n">
-        <v>79211</v>
+        <v>79219</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -844,10 +844,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>444973</v>
+        <v>444917</v>
       </c>
       <c r="R3" t="n">
-        <v>7052318</v>
+        <v>7052302</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -880,6 +880,11 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2026-01-16</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Relativt rikligt med garnlav på gran.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -895,11 +900,6 @@
       <c r="AH3" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AI3" t="inlineStr">
-        <is>
-          <t>Grandominerad äldre flerskiktad skog med inslag av björk.</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
@@ -940,7 +940,7 @@
         <v>130734159</v>
       </c>
       <c r="B4" t="n">
-        <v>79211</v>
+        <v>79219</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 61377-2025 artfynd.xlsx
+++ b/artfynd/A 61377-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>130734161</v>
+        <v>130734160</v>
       </c>
       <c r="B2" t="n">
-        <v>79219</v>
+        <v>79220</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -713,10 +713,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>444973</v>
+        <v>444917</v>
       </c>
       <c r="R2" t="n">
-        <v>7052318</v>
+        <v>7052302</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -749,6 +749,11 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2026-01-16</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Relativt rikligt med garnlav på gran.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -764,11 +769,6 @@
       <c r="AH2" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AI2" t="inlineStr">
-        <is>
-          <t>Grandominerad äldre flerskiktad skog med inslag av björk.</t>
         </is>
       </c>
       <c r="AJ2" t="inlineStr">
@@ -806,10 +806,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>130734160</v>
+        <v>130734161</v>
       </c>
       <c r="B3" t="n">
-        <v>79219</v>
+        <v>79220</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -844,10 +844,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>444917</v>
+        <v>444973</v>
       </c>
       <c r="R3" t="n">
-        <v>7052302</v>
+        <v>7052318</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -880,11 +880,6 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2026-01-16</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Relativt rikligt med garnlav på gran.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -900,6 +895,11 @@
       <c r="AH3" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AI3" t="inlineStr">
+        <is>
+          <t>Grandominerad äldre flerskiktad skog med inslag av björk.</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
@@ -940,7 +940,7 @@
         <v>130734159</v>
       </c>
       <c r="B4" t="n">
-        <v>79219</v>
+        <v>79220</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 61377-2025 artfynd.xlsx
+++ b/artfynd/A 61377-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>130734160</v>
       </c>
       <c r="B2" t="n">
-        <v>79220</v>
+        <v>79221</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -809,7 +809,7 @@
         <v>130734161</v>
       </c>
       <c r="B3" t="n">
-        <v>79220</v>
+        <v>79221</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -940,7 +940,7 @@
         <v>130734159</v>
       </c>
       <c r="B4" t="n">
-        <v>79220</v>
+        <v>79221</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 61377-2025 artfynd.xlsx
+++ b/artfynd/A 61377-2025 artfynd.xlsx
@@ -675,14 +675,14 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>130734160</v>
+        <v>130734159</v>
       </c>
       <c r="B2" t="n">
-        <v>79243</v>
+        <v>79327</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
@@ -713,10 +713,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>444917</v>
+        <v>444938</v>
       </c>
       <c r="R2" t="n">
-        <v>7052302</v>
+        <v>7052333</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -753,7 +753,7 @@
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>Relativt rikligt med garnlav på gran.</t>
+          <t>På flera granar.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -806,14 +806,14 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>130734161</v>
+        <v>130734160</v>
       </c>
       <c r="B3" t="n">
-        <v>79243</v>
+        <v>79327</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
@@ -844,10 +844,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>444973</v>
+        <v>444917</v>
       </c>
       <c r="R3" t="n">
-        <v>7052318</v>
+        <v>7052302</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -880,6 +880,11 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2026-01-16</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Relativt rikligt med garnlav på gran.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -895,11 +900,6 @@
       <c r="AH3" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AI3" t="inlineStr">
-        <is>
-          <t>Grandominerad äldre flerskiktad skog med inslag av björk.</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
@@ -937,14 +937,14 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>130734159</v>
+        <v>130734161</v>
       </c>
       <c r="B4" t="n">
-        <v>79243</v>
+        <v>79327</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
@@ -975,10 +975,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>444938</v>
+        <v>444973</v>
       </c>
       <c r="R4" t="n">
-        <v>7052333</v>
+        <v>7052318</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1011,11 +1011,6 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2026-01-16</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>På flera granar.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1031,6 +1026,11 @@
       <c r="AH4" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AI4" t="inlineStr">
+        <is>
+          <t>Grandominerad äldre flerskiktad skog med inslag av björk.</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
